--- a/data/matrix_time_minutes.xlsx
+++ b/data/matrix_time_minutes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FR174"/>
+  <dimension ref="A1:FY181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1282,6 +1282,41 @@
           <t>Pr002762</t>
         </is>
       </c>
+      <c r="FS1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FT1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FU1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FV1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FW1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FX1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FY1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1808,6 +1843,27 @@
       <c r="FR2" t="n">
         <v>10.01</v>
       </c>
+      <c r="FS2" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="FT2" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="FU2" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="FV2" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="FW2" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="FX2" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="FY2" t="n">
+        <v>2.54</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2334,6 +2390,27 @@
       <c r="FR3" t="n">
         <v>9.99</v>
       </c>
+      <c r="FS3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="FT3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="FU3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="FV3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="FW3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="FX3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="FY3" t="n">
+        <v>2.52</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2860,6 +2937,27 @@
       <c r="FR4" t="n">
         <v>10.01</v>
       </c>
+      <c r="FS4" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="FT4" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="FU4" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="FV4" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="FW4" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="FX4" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="FY4" t="n">
+        <v>2.54</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3386,6 +3484,27 @@
       <c r="FR5" t="n">
         <v>10.51</v>
       </c>
+      <c r="FS5" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="FT5" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="FU5" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="FV5" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="FW5" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="FX5" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="FY5" t="n">
+        <v>4.52</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3912,6 +4031,27 @@
       <c r="FR6" t="n">
         <v>13.17</v>
       </c>
+      <c r="FS6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="FT6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="FU6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="FV6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="FW6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="FX6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="FY6" t="n">
+        <v>5.7</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4438,6 +4578,27 @@
       <c r="FR7" t="n">
         <v>21.79</v>
       </c>
+      <c r="FS7" t="n">
+        <v>14.32</v>
+      </c>
+      <c r="FT7" t="n">
+        <v>14.32</v>
+      </c>
+      <c r="FU7" t="n">
+        <v>14.32</v>
+      </c>
+      <c r="FV7" t="n">
+        <v>14.32</v>
+      </c>
+      <c r="FW7" t="n">
+        <v>14.32</v>
+      </c>
+      <c r="FX7" t="n">
+        <v>14.32</v>
+      </c>
+      <c r="FY7" t="n">
+        <v>14.32</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4964,6 +5125,27 @@
       <c r="FR8" t="n">
         <v>14.54</v>
       </c>
+      <c r="FS8" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="FT8" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="FU8" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="FV8" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="FW8" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="FX8" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="FY8" t="n">
+        <v>7.07</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5490,6 +5672,27 @@
       <c r="FR9" t="n">
         <v>13.37</v>
       </c>
+      <c r="FS9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="FT9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="FU9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="FV9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="FW9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="FX9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="FY9" t="n">
+        <v>5.9</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6016,6 +6219,27 @@
       <c r="FR10" t="n">
         <v>13.4</v>
       </c>
+      <c r="FS10" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="FT10" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="FU10" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="FV10" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="FW10" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="FX10" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="FY10" t="n">
+        <v>5.93</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6542,6 +6766,27 @@
       <c r="FR11" t="n">
         <v>12.93</v>
       </c>
+      <c r="FS11" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="FT11" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="FU11" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="FV11" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="FW11" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="FX11" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="FY11" t="n">
+        <v>5.46</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7068,6 +7313,27 @@
       <c r="FR12" t="n">
         <v>9.99</v>
       </c>
+      <c r="FS12" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="FT12" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="FU12" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="FV12" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="FW12" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="FX12" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="FY12" t="n">
+        <v>2.52</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7594,6 +7860,27 @@
       <c r="FR13" t="n">
         <v>13.65</v>
       </c>
+      <c r="FS13" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="FT13" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="FU13" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="FV13" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="FW13" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="FX13" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="FY13" t="n">
+        <v>6.71</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8120,6 +8407,27 @@
       <c r="FR14" t="n">
         <v>12.28</v>
       </c>
+      <c r="FS14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="FT14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="FU14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="FV14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="FW14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="FX14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="FY14" t="n">
+        <v>4.8</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8646,6 +8954,27 @@
       <c r="FR15" t="n">
         <v>11.19</v>
       </c>
+      <c r="FS15" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="FT15" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="FU15" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="FV15" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="FW15" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="FX15" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="FY15" t="n">
+        <v>4.41</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9172,6 +9501,27 @@
       <c r="FR16" t="n">
         <v>10.8</v>
       </c>
+      <c r="FS16" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="FT16" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="FU16" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="FV16" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="FW16" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="FX16" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="FY16" t="n">
+        <v>4.71</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9698,6 +10048,27 @@
       <c r="FR17" t="n">
         <v>9.84</v>
       </c>
+      <c r="FS17" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="FT17" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="FU17" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="FV17" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="FW17" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="FX17" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="FY17" t="n">
+        <v>4.53</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -10224,6 +10595,27 @@
       <c r="FR18" t="n">
         <v>9.859999999999999</v>
       </c>
+      <c r="FS18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="FT18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="FU18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="FV18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="FW18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="FX18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="FY18" t="n">
+        <v>4.3</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -10750,6 +11142,27 @@
       <c r="FR19" t="n">
         <v>9.93</v>
       </c>
+      <c r="FS19" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="FT19" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="FU19" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="FV19" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="FW19" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="FX19" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="FY19" t="n">
+        <v>4.25</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -11276,6 +11689,27 @@
       <c r="FR20" t="n">
         <v>10.46</v>
       </c>
+      <c r="FS20" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="FT20" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="FU20" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="FV20" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="FW20" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="FX20" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="FY20" t="n">
+        <v>4.83</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -11802,6 +12236,27 @@
       <c r="FR21" t="n">
         <v>10.94</v>
       </c>
+      <c r="FS21" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="FT21" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="FU21" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="FV21" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="FW21" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="FX21" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="FY21" t="n">
+        <v>3.47</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -12328,6 +12783,27 @@
       <c r="FR22" t="n">
         <v>11.12</v>
       </c>
+      <c r="FS22" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="FT22" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="FU22" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="FV22" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="FW22" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="FX22" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="FY22" t="n">
+        <v>3.65</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -12854,6 +13330,27 @@
       <c r="FR23" t="n">
         <v>13.4</v>
       </c>
+      <c r="FS23" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="FT23" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="FU23" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="FV23" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="FW23" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="FX23" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="FY23" t="n">
+        <v>5.93</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -13380,6 +13877,27 @@
       <c r="FR24" t="n">
         <v>9.91</v>
       </c>
+      <c r="FS24" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="FT24" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="FU24" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="FV24" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="FW24" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="FX24" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="FY24" t="n">
+        <v>4.78</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -13906,6 +14424,27 @@
       <c r="FR25" t="n">
         <v>11.3</v>
       </c>
+      <c r="FS25" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="FT25" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="FU25" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="FV25" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="FW25" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="FX25" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="FY25" t="n">
+        <v>5.37</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -14432,6 +14971,27 @@
       <c r="FR26" t="n">
         <v>12.35</v>
       </c>
+      <c r="FS26" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="FT26" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="FU26" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="FV26" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="FW26" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="FX26" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="FY26" t="n">
+        <v>6.42</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -14958,6 +15518,27 @@
       <c r="FR27" t="n">
         <v>12.38</v>
       </c>
+      <c r="FS27" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="FT27" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="FU27" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="FV27" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="FW27" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="FX27" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="FY27" t="n">
+        <v>7.58</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -15484,6 +16065,27 @@
       <c r="FR28" t="n">
         <v>11.27</v>
       </c>
+      <c r="FS28" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="FT28" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="FU28" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="FV28" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="FW28" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="FX28" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="FY28" t="n">
+        <v>6.02</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -16010,6 +16612,27 @@
       <c r="FR29" t="n">
         <v>10.57</v>
       </c>
+      <c r="FS29" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="FT29" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="FU29" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="FV29" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="FW29" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="FX29" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="FY29" t="n">
+        <v>4.59</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -16536,6 +17159,27 @@
       <c r="FR30" t="n">
         <v>10.57</v>
       </c>
+      <c r="FS30" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="FT30" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="FU30" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="FV30" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="FW30" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="FX30" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="FY30" t="n">
+        <v>5.44</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -17062,6 +17706,27 @@
       <c r="FR31" t="n">
         <v>11.8</v>
       </c>
+      <c r="FS31" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="FT31" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="FU31" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="FV31" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="FW31" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="FX31" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="FY31" t="n">
+        <v>5.87</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -17588,6 +18253,27 @@
       <c r="FR32" t="n">
         <v>11.99</v>
       </c>
+      <c r="FS32" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="FT32" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="FU32" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="FV32" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="FW32" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="FX32" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="FY32" t="n">
+        <v>6.06</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -18114,6 +18800,27 @@
       <c r="FR33" t="n">
         <v>11.7</v>
       </c>
+      <c r="FS33" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="FT33" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="FU33" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="FV33" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="FW33" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="FX33" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="FY33" t="n">
+        <v>5.77</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -18640,6 +19347,27 @@
       <c r="FR34" t="n">
         <v>11.54</v>
       </c>
+      <c r="FS34" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="FT34" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="FU34" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="FV34" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="FW34" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="FX34" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="FY34" t="n">
+        <v>6.55</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -19166,6 +19894,27 @@
       <c r="FR35" t="n">
         <v>12.07</v>
       </c>
+      <c r="FS35" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="FT35" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="FU35" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="FV35" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="FW35" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="FX35" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="FY35" t="n">
+        <v>7.24</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -19692,6 +20441,27 @@
       <c r="FR36" t="n">
         <v>10.78</v>
       </c>
+      <c r="FS36" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="FT36" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="FU36" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="FV36" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="FW36" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="FX36" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="FY36" t="n">
+        <v>4.85</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -20218,6 +20988,27 @@
       <c r="FR37" t="n">
         <v>11.46</v>
       </c>
+      <c r="FS37" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="FT37" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="FU37" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="FV37" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="FW37" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="FX37" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="FY37" t="n">
+        <v>5.6</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -20744,6 +21535,27 @@
       <c r="FR38" t="n">
         <v>10.71</v>
       </c>
+      <c r="FS38" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="FT38" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="FU38" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="FV38" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="FW38" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="FX38" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="FY38" t="n">
+        <v>4.85</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -21270,6 +22082,27 @@
       <c r="FR39" t="n">
         <v>11.19</v>
       </c>
+      <c r="FS39" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="FT39" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="FU39" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="FV39" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="FW39" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="FX39" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="FY39" t="n">
+        <v>5.77</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -21796,6 +22629,27 @@
       <c r="FR40" t="n">
         <v>11.24</v>
       </c>
+      <c r="FS40" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="FT40" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="FU40" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="FV40" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="FW40" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="FX40" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="FY40" t="n">
+        <v>4.78</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -22322,6 +23176,27 @@
       <c r="FR41" t="n">
         <v>12.28</v>
       </c>
+      <c r="FS41" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="FT41" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="FU41" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="FV41" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="FW41" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="FX41" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="FY41" t="n">
+        <v>4.8</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -22848,6 +23723,27 @@
       <c r="FR42" t="n">
         <v>10.3</v>
       </c>
+      <c r="FS42" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="FT42" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="FU42" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="FV42" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="FW42" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="FX42" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="FY42" t="n">
+        <v>4.25</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -23374,6 +24270,27 @@
       <c r="FR43" t="n">
         <v>10.59</v>
       </c>
+      <c r="FS43" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="FT43" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="FU43" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="FV43" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="FW43" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="FX43" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="FY43" t="n">
+        <v>4.54</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -23900,6 +24817,27 @@
       <c r="FR44" t="n">
         <v>10.53</v>
       </c>
+      <c r="FS44" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="FT44" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="FU44" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="FV44" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="FW44" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="FX44" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="FY44" t="n">
+        <v>4.93</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -24426,6 +25364,27 @@
       <c r="FR45" t="n">
         <v>11.99</v>
       </c>
+      <c r="FS45" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="FT45" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="FU45" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="FV45" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="FW45" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="FX45" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="FY45" t="n">
+        <v>6.06</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -24952,6 +25911,27 @@
       <c r="FR46" t="n">
         <v>9.02</v>
       </c>
+      <c r="FS46" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="FT46" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="FU46" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="FV46" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="FW46" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="FX46" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="FY46" t="n">
+        <v>4.05</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -25478,6 +26458,27 @@
       <c r="FR47" t="n">
         <v>9.949999999999999</v>
       </c>
+      <c r="FS47" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="FT47" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="FU47" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="FV47" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="FW47" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="FX47" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="FY47" t="n">
+        <v>3.93</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -26004,6 +27005,27 @@
       <c r="FR48" t="n">
         <v>9.949999999999999</v>
       </c>
+      <c r="FS48" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="FT48" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="FU48" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="FV48" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="FW48" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="FX48" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="FY48" t="n">
+        <v>3.93</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -26530,6 +27552,27 @@
       <c r="FR49" t="n">
         <v>9.82</v>
       </c>
+      <c r="FS49" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="FT49" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="FU49" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="FV49" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="FW49" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="FX49" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="FY49" t="n">
+        <v>4.69</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -27056,6 +28099,27 @@
       <c r="FR50" t="n">
         <v>11.4</v>
       </c>
+      <c r="FS50" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="FT50" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="FU50" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="FV50" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="FW50" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="FX50" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="FY50" t="n">
+        <v>6.84</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -27582,6 +28646,27 @@
       <c r="FR51" t="n">
         <v>11.96</v>
       </c>
+      <c r="FS51" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="FT51" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="FU51" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="FV51" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="FW51" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="FX51" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="FY51" t="n">
+        <v>7.19</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -28108,6 +29193,27 @@
       <c r="FR52" t="n">
         <v>11.48</v>
       </c>
+      <c r="FS52" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="FT52" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="FU52" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="FV52" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="FW52" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="FX52" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="FY52" t="n">
+        <v>7.47</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -28634,6 +29740,27 @@
       <c r="FR53" t="n">
         <v>10.31</v>
       </c>
+      <c r="FS53" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="FT53" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="FU53" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="FV53" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="FW53" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="FX53" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="FY53" t="n">
+        <v>7.88</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -29160,6 +30287,27 @@
       <c r="FR54" t="n">
         <v>13.3</v>
       </c>
+      <c r="FS54" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="FT54" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="FU54" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="FV54" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="FW54" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="FX54" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="FY54" t="n">
+        <v>15.9</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -29686,6 +30834,27 @@
       <c r="FR55" t="n">
         <v>13.2</v>
       </c>
+      <c r="FS55" t="n">
+        <v>15.79</v>
+      </c>
+      <c r="FT55" t="n">
+        <v>15.79</v>
+      </c>
+      <c r="FU55" t="n">
+        <v>15.79</v>
+      </c>
+      <c r="FV55" t="n">
+        <v>15.79</v>
+      </c>
+      <c r="FW55" t="n">
+        <v>15.79</v>
+      </c>
+      <c r="FX55" t="n">
+        <v>15.79</v>
+      </c>
+      <c r="FY55" t="n">
+        <v>15.79</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -30212,6 +31381,27 @@
       <c r="FR56" t="n">
         <v>11.92</v>
       </c>
+      <c r="FS56" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="FT56" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="FU56" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="FV56" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="FW56" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="FX56" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="FY56" t="n">
+        <v>10.32</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -30738,6 +31928,27 @@
       <c r="FR57" t="n">
         <v>11.92</v>
       </c>
+      <c r="FS57" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="FT57" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="FU57" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="FV57" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="FW57" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="FX57" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="FY57" t="n">
+        <v>10.32</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -31264,6 +32475,27 @@
       <c r="FR58" t="n">
         <v>11.19</v>
       </c>
+      <c r="FS58" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="FT58" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="FU58" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="FV58" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="FW58" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="FX58" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="FY58" t="n">
+        <v>6.28</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -31790,6 +33022,27 @@
       <c r="FR59" t="n">
         <v>12.07</v>
       </c>
+      <c r="FS59" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="FT59" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="FU59" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="FV59" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="FW59" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="FX59" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="FY59" t="n">
+        <v>7.24</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -32316,6 +33569,27 @@
       <c r="FR60" t="n">
         <v>12.33</v>
       </c>
+      <c r="FS60" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="FT60" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="FU60" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="FV60" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="FW60" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="FX60" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="FY60" t="n">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -32842,6 +34116,27 @@
       <c r="FR61" t="n">
         <v>11.38</v>
       </c>
+      <c r="FS61" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="FT61" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="FU61" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="FV61" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="FW61" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="FX61" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="FY61" t="n">
+        <v>7.39</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -33368,6 +34663,27 @@
       <c r="FR62" t="n">
         <v>11.38</v>
       </c>
+      <c r="FS62" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="FT62" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="FU62" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="FV62" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="FW62" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="FX62" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="FY62" t="n">
+        <v>7.39</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -33894,6 +35210,27 @@
       <c r="FR63" t="n">
         <v>9.9</v>
       </c>
+      <c r="FS63" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="FT63" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="FU63" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="FV63" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="FW63" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="FX63" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="FY63" t="n">
+        <v>7.79</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -34420,6 +35757,27 @@
       <c r="FR64" t="n">
         <v>10.51</v>
       </c>
+      <c r="FS64" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="FT64" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="FU64" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="FV64" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="FW64" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="FX64" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="FY64" t="n">
+        <v>8.199999999999999</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -34946,6 +36304,27 @@
       <c r="FR65" t="n">
         <v>11.01</v>
       </c>
+      <c r="FS65" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="FT65" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="FU65" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="FV65" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="FW65" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="FX65" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="FY65" t="n">
+        <v>7.81</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -35472,6 +36851,27 @@
       <c r="FR66" t="n">
         <v>11.01</v>
       </c>
+      <c r="FS66" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="FT66" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="FU66" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="FV66" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="FW66" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="FX66" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="FY66" t="n">
+        <v>7.81</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -35998,6 +37398,27 @@
       <c r="FR67" t="n">
         <v>11.76</v>
       </c>
+      <c r="FS67" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="FT67" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="FU67" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="FV67" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="FW67" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="FX67" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="FY67" t="n">
+        <v>7.67</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -36524,6 +37945,27 @@
       <c r="FR68" t="n">
         <v>12.42</v>
       </c>
+      <c r="FS68" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="FT68" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="FU68" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="FV68" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="FW68" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="FX68" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="FY68" t="n">
+        <v>7.82</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -37050,6 +38492,27 @@
       <c r="FR69" t="n">
         <v>12.48</v>
       </c>
+      <c r="FS69" t="n">
+        <v>8</v>
+      </c>
+      <c r="FT69" t="n">
+        <v>8</v>
+      </c>
+      <c r="FU69" t="n">
+        <v>8</v>
+      </c>
+      <c r="FV69" t="n">
+        <v>8</v>
+      </c>
+      <c r="FW69" t="n">
+        <v>8</v>
+      </c>
+      <c r="FX69" t="n">
+        <v>8</v>
+      </c>
+      <c r="FY69" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -37576,6 +39039,27 @@
       <c r="FR70" t="n">
         <v>12.8</v>
       </c>
+      <c r="FS70" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="FT70" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="FU70" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="FV70" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="FW70" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="FX70" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="FY70" t="n">
+        <v>8.119999999999999</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -38102,6 +39586,27 @@
       <c r="FR71" t="n">
         <v>12.57</v>
       </c>
+      <c r="FS71" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="FT71" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="FU71" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="FV71" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="FW71" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="FX71" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="FY71" t="n">
+        <v>7.74</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -38628,6 +40133,27 @@
       <c r="FR72" t="n">
         <v>12.35</v>
       </c>
+      <c r="FS72" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="FT72" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="FU72" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="FV72" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="FW72" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="FX72" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="FY72" t="n">
+        <v>7.03</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -39154,6 +40680,27 @@
       <c r="FR73" t="n">
         <v>11.99</v>
       </c>
+      <c r="FS73" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="FT73" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="FU73" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="FV73" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="FW73" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="FX73" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="FY73" t="n">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -39680,6 +41227,27 @@
       <c r="FR74" t="n">
         <v>12.72</v>
       </c>
+      <c r="FS74" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="FT74" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="FU74" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="FV74" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="FW74" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="FX74" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="FY74" t="n">
+        <v>7.24</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -40206,6 +41774,27 @@
       <c r="FR75" t="n">
         <v>10.19</v>
       </c>
+      <c r="FS75" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="FT75" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="FU75" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="FV75" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="FW75" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="FX75" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="FY75" t="n">
+        <v>6.97</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -40732,6 +42321,27 @@
       <c r="FR76" t="n">
         <v>7.93</v>
       </c>
+      <c r="FS76" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="FT76" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="FU76" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="FV76" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="FW76" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="FX76" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="FY76" t="n">
+        <v>2.76</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -41258,6 +42868,27 @@
       <c r="FR77" t="n">
         <v>6.24</v>
       </c>
+      <c r="FS77" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="FT77" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="FU77" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="FV77" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="FW77" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="FX77" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="FY77" t="n">
+        <v>5.06</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -41784,6 +43415,27 @@
       <c r="FR78" t="n">
         <v>8.44</v>
       </c>
+      <c r="FS78" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="FT78" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="FU78" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="FV78" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="FW78" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="FX78" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="FY78" t="n">
+        <v>4.33</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -42310,6 +43962,27 @@
       <c r="FR79" t="n">
         <v>8.539999999999999</v>
       </c>
+      <c r="FS79" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="FT79" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="FU79" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="FV79" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="FW79" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="FX79" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="FY79" t="n">
+        <v>6.98</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -42836,6 +44509,27 @@
       <c r="FR80" t="n">
         <v>6.94</v>
       </c>
+      <c r="FS80" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="FT80" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="FU80" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="FV80" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="FW80" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="FX80" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="FY80" t="n">
+        <v>5.08</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -43362,6 +45056,27 @@
       <c r="FR81" t="n">
         <v>7.05</v>
       </c>
+      <c r="FS81" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="FT81" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="FU81" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="FV81" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="FW81" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="FX81" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="FY81" t="n">
+        <v>5.89</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -43888,6 +45603,27 @@
       <c r="FR82" t="n">
         <v>6.61</v>
       </c>
+      <c r="FS82" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="FT82" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="FU82" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="FV82" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="FW82" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="FX82" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="FY82" t="n">
+        <v>5.73</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -44414,6 +46150,27 @@
       <c r="FR83" t="n">
         <v>6.46</v>
       </c>
+      <c r="FS83" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="FT83" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="FU83" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="FV83" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="FW83" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="FX83" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="FY83" t="n">
+        <v>5.29</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -44940,6 +46697,27 @@
       <c r="FR84" t="n">
         <v>6.62</v>
       </c>
+      <c r="FS84" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="FT84" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="FU84" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="FV84" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="FW84" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="FX84" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="FY84" t="n">
+        <v>5.46</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -45466,6 +47244,27 @@
       <c r="FR85" t="n">
         <v>7.28</v>
       </c>
+      <c r="FS85" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="FT85" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="FU85" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="FV85" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="FW85" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="FX85" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="FY85" t="n">
+        <v>5.42</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -45992,6 +47791,27 @@
       <c r="FR86" t="n">
         <v>4.63</v>
       </c>
+      <c r="FS86" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="FT86" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="FU86" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="FV86" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="FW86" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="FX86" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="FY86" t="n">
+        <v>6.01</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -46518,6 +48338,27 @@
       <c r="FR87" t="n">
         <v>4</v>
       </c>
+      <c r="FS87" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="FT87" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="FU87" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="FV87" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="FW87" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="FX87" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="FY87" t="n">
+        <v>6.64</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -47044,6 +48885,27 @@
       <c r="FR88" t="n">
         <v>6.31</v>
       </c>
+      <c r="FS88" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="FT88" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="FU88" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="FV88" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="FW88" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="FX88" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="FY88" t="n">
+        <v>5.09</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -47570,6 +49432,27 @@
       <c r="FR89" t="n">
         <v>6.43</v>
       </c>
+      <c r="FS89" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="FT89" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="FU89" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="FV89" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="FW89" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="FX89" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="FY89" t="n">
+        <v>4.74</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -48096,6 +49979,27 @@
       <c r="FR90" t="n">
         <v>5.11</v>
       </c>
+      <c r="FS90" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="FT90" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="FU90" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="FV90" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="FW90" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="FX90" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="FY90" t="n">
+        <v>6.08</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -48622,6 +50526,27 @@
       <c r="FR91" t="n">
         <v>6.71</v>
       </c>
+      <c r="FS91" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="FT91" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="FU91" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="FV91" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="FW91" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="FX91" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="FY91" t="n">
+        <v>4.3</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -49148,6 +51073,27 @@
       <c r="FR92" t="n">
         <v>6.7</v>
       </c>
+      <c r="FS92" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="FT92" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="FU92" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="FV92" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="FW92" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="FX92" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="FY92" t="n">
+        <v>4.31</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -49674,6 +51620,27 @@
       <c r="FR93" t="n">
         <v>7.79</v>
       </c>
+      <c r="FS93" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="FT93" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="FU93" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="FV93" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="FW93" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="FX93" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="FY93" t="n">
+        <v>3.54</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -50200,6 +52167,27 @@
       <c r="FR94" t="n">
         <v>9.039999999999999</v>
       </c>
+      <c r="FS94" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="FT94" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="FU94" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="FV94" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="FW94" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="FX94" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="FY94" t="n">
+        <v>2.56</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -50726,6 +52714,27 @@
       <c r="FR95" t="n">
         <v>7.83</v>
       </c>
+      <c r="FS95" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="FT95" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="FU95" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="FV95" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="FW95" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="FX95" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="FY95" t="n">
+        <v>3.15</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -51252,6 +53261,27 @@
       <c r="FR96" t="n">
         <v>6.88</v>
       </c>
+      <c r="FS96" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="FT96" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="FU96" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="FV96" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="FW96" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="FX96" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="FY96" t="n">
+        <v>3.82</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -51778,6 +53808,27 @@
       <c r="FR97" t="n">
         <v>7.17</v>
       </c>
+      <c r="FS97" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="FT97" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="FU97" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="FV97" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="FW97" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="FX97" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="FY97" t="n">
+        <v>3.52</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -52304,6 +54355,27 @@
       <c r="FR98" t="n">
         <v>7.02</v>
       </c>
+      <c r="FS98" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="FT98" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="FU98" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="FV98" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="FW98" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="FX98" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="FY98" t="n">
+        <v>3.76</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -52830,6 +54902,27 @@
       <c r="FR99" t="n">
         <v>8.1</v>
       </c>
+      <c r="FS99" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="FT99" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="FU99" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="FV99" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="FW99" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="FX99" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="FY99" t="n">
+        <v>3.18</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -53356,6 +55449,27 @@
       <c r="FR100" t="n">
         <v>8.869999999999999</v>
       </c>
+      <c r="FS100" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="FT100" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="FU100" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="FV100" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="FW100" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="FX100" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="FY100" t="n">
+        <v>3.04</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -53882,6 +55996,27 @@
       <c r="FR101" t="n">
         <v>10.98</v>
       </c>
+      <c r="FS101" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="FT101" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="FU101" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="FV101" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="FW101" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="FX101" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="FY101" t="n">
+        <v>1.72</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -54408,6 +56543,27 @@
       <c r="FR102" t="n">
         <v>11.32</v>
       </c>
+      <c r="FS102" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="FT102" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="FU102" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="FV102" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="FW102" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="FX102" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="FY102" t="n">
+        <v>3.64</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -54934,6 +57090,27 @@
       <c r="FR103" t="n">
         <v>19.61</v>
       </c>
+      <c r="FS103" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="FT103" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="FU103" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="FV103" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="FW103" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="FX103" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="FY103" t="n">
+        <v>11.73</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -55460,6 +57637,27 @@
       <c r="FR104" t="n">
         <v>11.11</v>
       </c>
+      <c r="FS104" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="FT104" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="FU104" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="FV104" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="FW104" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="FX104" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="FY104" t="n">
+        <v>2.75</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -55986,6 +58184,27 @@
       <c r="FR105" t="n">
         <v>11.29</v>
       </c>
+      <c r="FS105" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="FT105" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="FU105" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="FV105" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="FW105" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="FX105" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="FY105" t="n">
+        <v>2.94</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -56512,6 +58731,27 @@
       <c r="FR106" t="n">
         <v>12.81</v>
       </c>
+      <c r="FS106" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="FT106" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="FU106" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="FV106" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="FW106" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="FX106" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="FY106" t="n">
+        <v>7.95</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -57038,6 +59278,27 @@
       <c r="FR107" t="n">
         <v>11.13</v>
       </c>
+      <c r="FS107" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="FT107" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="FU107" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="FV107" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="FW107" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="FX107" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="FY107" t="n">
+        <v>2.78</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -57564,6 +59825,27 @@
       <c r="FR108" t="n">
         <v>11.53</v>
       </c>
+      <c r="FS108" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="FT108" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="FU108" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="FV108" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="FW108" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="FX108" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="FY108" t="n">
+        <v>3.28</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -58090,6 +60372,27 @@
       <c r="FR109" t="n">
         <v>13.17</v>
       </c>
+      <c r="FS109" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="FT109" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="FU109" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="FV109" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="FW109" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="FX109" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="FY109" t="n">
+        <v>4.93</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -58616,6 +60919,27 @@
       <c r="FR110" t="n">
         <v>14.26</v>
       </c>
+      <c r="FS110" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="FT110" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="FU110" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="FV110" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="FW110" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="FX110" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="FY110" t="n">
+        <v>6.53</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -59142,6 +61466,27 @@
       <c r="FR111" t="n">
         <v>14.46</v>
       </c>
+      <c r="FS111" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="FT111" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="FU111" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="FV111" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="FW111" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="FX111" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="FY111" t="n">
+        <v>6.73</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -59668,6 +62013,27 @@
       <c r="FR112" t="n">
         <v>12.84</v>
       </c>
+      <c r="FS112" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="FT112" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="FU112" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="FV112" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="FW112" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="FX112" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="FY112" t="n">
+        <v>5.11</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -60194,6 +62560,27 @@
       <c r="FR113" t="n">
         <v>14.02</v>
       </c>
+      <c r="FS113" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="FT113" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="FU113" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="FV113" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="FW113" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="FX113" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="FY113" t="n">
+        <v>6.29</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -60720,6 +63107,27 @@
       <c r="FR114" t="n">
         <v>13.56</v>
       </c>
+      <c r="FS114" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="FT114" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="FU114" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="FV114" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="FW114" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="FX114" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="FY114" t="n">
+        <v>5.83</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -61246,6 +63654,27 @@
       <c r="FR115" t="n">
         <v>10.66</v>
       </c>
+      <c r="FS115" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="FT115" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="FU115" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="FV115" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="FW115" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="FX115" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="FY115" t="n">
+        <v>3.54</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -61772,6 +64201,27 @@
       <c r="FR116" t="n">
         <v>11.1</v>
       </c>
+      <c r="FS116" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="FT116" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="FU116" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="FV116" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="FW116" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="FX116" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="FY116" t="n">
+        <v>3.63</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -62298,6 +64748,27 @@
       <c r="FR117" t="n">
         <v>11.38</v>
       </c>
+      <c r="FS117" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="FT117" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="FU117" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="FV117" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="FW117" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="FX117" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="FY117" t="n">
+        <v>3.22</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -62824,6 +65295,27 @@
       <c r="FR118" t="n">
         <v>14.34</v>
       </c>
+      <c r="FS118" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="FT118" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="FU118" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="FV118" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="FW118" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="FX118" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="FY118" t="n">
+        <v>6.46</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -63350,6 +65842,27 @@
       <c r="FR119" t="n">
         <v>13.85</v>
       </c>
+      <c r="FS119" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="FT119" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="FU119" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="FV119" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="FW119" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="FX119" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="FY119" t="n">
+        <v>5.97</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -63876,6 +66389,27 @@
       <c r="FR120" t="n">
         <v>16.24</v>
       </c>
+      <c r="FS120" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="FT120" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="FU120" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="FV120" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="FW120" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="FX120" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="FY120" t="n">
+        <v>8.359999999999999</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -64402,6 +66936,27 @@
       <c r="FR121" t="n">
         <v>13.43</v>
       </c>
+      <c r="FS121" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="FT121" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="FU121" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="FV121" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="FW121" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="FX121" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="FY121" t="n">
+        <v>5.55</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -64928,6 +67483,27 @@
       <c r="FR122" t="n">
         <v>13.21</v>
       </c>
+      <c r="FS122" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="FT122" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="FU122" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="FV122" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="FW122" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="FX122" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="FY122" t="n">
+        <v>5.33</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -65454,6 +68030,27 @@
       <c r="FR123" t="n">
         <v>13.31</v>
       </c>
+      <c r="FS123" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="FT123" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="FU123" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="FV123" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="FW123" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="FX123" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="FY123" t="n">
+        <v>5.43</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -65980,6 +68577,27 @@
       <c r="FR124" t="n">
         <v>12.93</v>
       </c>
+      <c r="FS124" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="FT124" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="FU124" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="FV124" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="FW124" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="FX124" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="FY124" t="n">
+        <v>5.05</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -66506,6 +69124,27 @@
       <c r="FR125" t="n">
         <v>11.49</v>
       </c>
+      <c r="FS125" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="FT125" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="FU125" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="FV125" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="FW125" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="FX125" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="FY125" t="n">
+        <v>3.13</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -67032,6 +69671,27 @@
       <c r="FR126" t="n">
         <v>11.29</v>
       </c>
+      <c r="FS126" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="FT126" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="FU126" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="FV126" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="FW126" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="FX126" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="FY126" t="n">
+        <v>2.94</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -67558,6 +70218,27 @@
       <c r="FR127" t="n">
         <v>11.31</v>
       </c>
+      <c r="FS127" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="FT127" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="FU127" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="FV127" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="FW127" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="FX127" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="FY127" t="n">
+        <v>3.43</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -68084,6 +70765,27 @@
       <c r="FR128" t="n">
         <v>10.2</v>
       </c>
+      <c r="FS128" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="FT128" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="FU128" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="FV128" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="FW128" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="FX128" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="FY128" t="n">
+        <v>4.57</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -68610,6 +71312,27 @@
       <c r="FR129" t="n">
         <v>10.27</v>
       </c>
+      <c r="FS129" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="FT129" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="FU129" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="FV129" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="FW129" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="FX129" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="FY129" t="n">
+        <v>4.02</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -69136,6 +71859,27 @@
       <c r="FR130" t="n">
         <v>10.03</v>
       </c>
+      <c r="FS130" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="FT130" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="FU130" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="FV130" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="FW130" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="FX130" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="FY130" t="n">
+        <v>4.35</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -69662,6 +72406,27 @@
       <c r="FR131" t="n">
         <v>13.4</v>
       </c>
+      <c r="FS131" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="FT131" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="FU131" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="FV131" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="FW131" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="FX131" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="FY131" t="n">
+        <v>6.44</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -70188,6 +72953,27 @@
       <c r="FR132" t="n">
         <v>12.81</v>
       </c>
+      <c r="FS132" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="FT132" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="FU132" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="FV132" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="FW132" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="FX132" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="FY132" t="n">
+        <v>6.34</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -70714,6 +73500,27 @@
       <c r="FR133" t="n">
         <v>13.63</v>
       </c>
+      <c r="FS133" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="FT133" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="FU133" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="FV133" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="FW133" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="FX133" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="FY133" t="n">
+        <v>7.17</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -71240,6 +74047,27 @@
       <c r="FR134" t="n">
         <v>13.31</v>
       </c>
+      <c r="FS134" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="FT134" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="FU134" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="FV134" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="FW134" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="FX134" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="FY134" t="n">
+        <v>6.85</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -71766,6 +74594,27 @@
       <c r="FR135" t="n">
         <v>12.14</v>
       </c>
+      <c r="FS135" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="FT135" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="FU135" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="FV135" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="FW135" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="FX135" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="FY135" t="n">
+        <v>5.67</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -72292,6 +75141,27 @@
       <c r="FR136" t="n">
         <v>14.18</v>
       </c>
+      <c r="FS136" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="FT136" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="FU136" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="FV136" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="FW136" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="FX136" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="FY136" t="n">
+        <v>7.71</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -72818,6 +75688,27 @@
       <c r="FR137" t="n">
         <v>14.89</v>
       </c>
+      <c r="FS137" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="FT137" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="FU137" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="FV137" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="FW137" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="FX137" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="FY137" t="n">
+        <v>8.42</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -73344,6 +76235,27 @@
       <c r="FR138" t="n">
         <v>12.56</v>
       </c>
+      <c r="FS138" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="FT138" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="FU138" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="FV138" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="FW138" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="FX138" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="FY138" t="n">
+        <v>6.1</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -73870,6 +76782,27 @@
       <c r="FR139" t="n">
         <v>14.52</v>
       </c>
+      <c r="FS139" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="FT139" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="FU139" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="FV139" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="FW139" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="FX139" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="FY139" t="n">
+        <v>8.050000000000001</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -74396,6 +77329,27 @@
       <c r="FR140" t="n">
         <v>15.67</v>
       </c>
+      <c r="FS140" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="FT140" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="FU140" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="FV140" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="FW140" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="FX140" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="FY140" t="n">
+        <v>9.199999999999999</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -74922,6 +77876,27 @@
       <c r="FR141" t="n">
         <v>13.9</v>
       </c>
+      <c r="FS141" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="FT141" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="FU141" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="FV141" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="FW141" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="FX141" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="FY141" t="n">
+        <v>7.43</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -75448,6 +78423,27 @@
       <c r="FR142" t="n">
         <v>15.34</v>
       </c>
+      <c r="FS142" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="FT142" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="FU142" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="FV142" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="FW142" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="FX142" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="FY142" t="n">
+        <v>8.869999999999999</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -75974,6 +78970,27 @@
       <c r="FR143" t="n">
         <v>12.8</v>
       </c>
+      <c r="FS143" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="FT143" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="FU143" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="FV143" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="FW143" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="FX143" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="FY143" t="n">
+        <v>6.33</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -76500,6 +79517,27 @@
       <c r="FR144" t="n">
         <v>10.81</v>
       </c>
+      <c r="FS144" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="FT144" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="FU144" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="FV144" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="FW144" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="FX144" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="FY144" t="n">
+        <v>4.76</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -77026,6 +80064,27 @@
       <c r="FR145" t="n">
         <v>10.98</v>
       </c>
+      <c r="FS145" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="FT145" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="FU145" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="FV145" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="FW145" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="FX145" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="FY145" t="n">
+        <v>4.24</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -77552,6 +80611,27 @@
       <c r="FR146" t="n">
         <v>10.93</v>
       </c>
+      <c r="FS146" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="FT146" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="FU146" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="FV146" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="FW146" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="FX146" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="FY146" t="n">
+        <v>3.73</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -78078,6 +81158,27 @@
       <c r="FR147" t="n">
         <v>10.5</v>
       </c>
+      <c r="FS147" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="FT147" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="FU147" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="FV147" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="FW147" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="FX147" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="FY147" t="n">
+        <v>3.3</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -78604,6 +81705,27 @@
       <c r="FR148" t="n">
         <v>10.54</v>
       </c>
+      <c r="FS148" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="FT148" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="FU148" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="FV148" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="FW148" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="FX148" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="FY148" t="n">
+        <v>3.07</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -79130,6 +82252,27 @@
       <c r="FR149" t="n">
         <v>10.03</v>
       </c>
+      <c r="FS149" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="FT149" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="FU149" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="FV149" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="FW149" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="FX149" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="FY149" t="n">
+        <v>2.56</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -79656,6 +82799,27 @@
       <c r="FR150" t="n">
         <v>10.02</v>
       </c>
+      <c r="FS150" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="FT150" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="FU150" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="FV150" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="FW150" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="FX150" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="FY150" t="n">
+        <v>2.55</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -80182,6 +83346,27 @@
       <c r="FR151" t="n">
         <v>10.19</v>
       </c>
+      <c r="FS151" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="FT151" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="FU151" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="FV151" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="FW151" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="FX151" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="FY151" t="n">
+        <v>2.72</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -80708,6 +83893,27 @@
       <c r="FR152" t="n">
         <v>9.390000000000001</v>
       </c>
+      <c r="FS152" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="FT152" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="FU152" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="FV152" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="FW152" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="FX152" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="FY152" t="n">
+        <v>1.92</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -81234,6 +84440,27 @@
       <c r="FR153" t="n">
         <v>8.369999999999999</v>
       </c>
+      <c r="FS153" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="FT153" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="FU153" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="FV153" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="FW153" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="FX153" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="FY153" t="n">
+        <v>2.3</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -81760,6 +84987,27 @@
       <c r="FR154" t="n">
         <v>9.01</v>
       </c>
+      <c r="FS154" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="FT154" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="FU154" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="FV154" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="FW154" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="FX154" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="FY154" t="n">
+        <v>2.29</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -82286,6 +85534,27 @@
       <c r="FR155" t="n">
         <v>9.5</v>
       </c>
+      <c r="FS155" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="FT155" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="FU155" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="FV155" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="FW155" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="FX155" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="FY155" t="n">
+        <v>2.49</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -82812,6 +86081,27 @@
       <c r="FR156" t="n">
         <v>5.83</v>
       </c>
+      <c r="FS156" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="FT156" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="FU156" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="FV156" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="FW156" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="FX156" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="FY156" t="n">
+        <v>4.81</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -83338,6 +86628,27 @@
       <c r="FR157" t="n">
         <v>4.36</v>
       </c>
+      <c r="FS157" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="FT157" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="FU157" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="FV157" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="FW157" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="FX157" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="FY157" t="n">
+        <v>6.54</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -83864,6 +87175,27 @@
       <c r="FR158" t="n">
         <v>1.6</v>
       </c>
+      <c r="FS158" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="FT158" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="FU158" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="FV158" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="FW158" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="FX158" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="FY158" t="n">
+        <v>11.91</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -84390,6 +87722,27 @@
       <c r="FR159" t="n">
         <v>0.92</v>
       </c>
+      <c r="FS159" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="FT159" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="FU159" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="FV159" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="FW159" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="FX159" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="FY159" t="n">
+        <v>10.36</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -84916,6 +88269,27 @@
       <c r="FR160" t="n">
         <v>1.66</v>
       </c>
+      <c r="FS160" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="FT160" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="FU160" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="FV160" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="FW160" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="FX160" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="FY160" t="n">
+        <v>10.96</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -85442,6 +88816,27 @@
       <c r="FR161" t="n">
         <v>1.86</v>
       </c>
+      <c r="FS161" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="FT161" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="FU161" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="FV161" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="FW161" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="FX161" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="FY161" t="n">
+        <v>10.56</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -85968,6 +89363,27 @@
       <c r="FR162" t="n">
         <v>2.34</v>
       </c>
+      <c r="FS162" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="FT162" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="FU162" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="FV162" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="FW162" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="FX162" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="FY162" t="n">
+        <v>8.92</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -86494,6 +89910,27 @@
       <c r="FR163" t="n">
         <v>5.56</v>
       </c>
+      <c r="FS163" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="FT163" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="FU163" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="FV163" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="FW163" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="FX163" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="FY163" t="n">
+        <v>5.32</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -87020,6 +90457,27 @@
       <c r="FR164" t="n">
         <v>7.07</v>
       </c>
+      <c r="FS164" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="FT164" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="FU164" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="FV164" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="FW164" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="FX164" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="FY164" t="n">
+        <v>4.14</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -87546,6 +91004,27 @@
       <c r="FR165" t="n">
         <v>9.69</v>
       </c>
+      <c r="FS165" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="FT165" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="FU165" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="FV165" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="FW165" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="FX165" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="FY165" t="n">
+        <v>2.63</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -88072,6 +91551,27 @@
       <c r="FR166" t="n">
         <v>9.26</v>
       </c>
+      <c r="FS166" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="FT166" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="FU166" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="FV166" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="FW166" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="FX166" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="FY166" t="n">
+        <v>1.92</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -88598,6 +92098,27 @@
       <c r="FR167" t="n">
         <v>8.9</v>
       </c>
+      <c r="FS167" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="FT167" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="FU167" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="FV167" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="FW167" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="FX167" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="FY167" t="n">
+        <v>3.25</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -89124,6 +92645,27 @@
       <c r="FR168" t="n">
         <v>9.92</v>
       </c>
+      <c r="FS168" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="FT168" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="FU168" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="FV168" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="FW168" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="FX168" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="FY168" t="n">
+        <v>3.29</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -89650,6 +93192,27 @@
       <c r="FR169" t="n">
         <v>10.15</v>
       </c>
+      <c r="FS169" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="FT169" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="FU169" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="FV169" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="FW169" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="FX169" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="FY169" t="n">
+        <v>3.16</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -90176,6 +93739,27 @@
       <c r="FR170" t="n">
         <v>10.48</v>
       </c>
+      <c r="FS170" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="FT170" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="FU170" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="FV170" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="FW170" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="FX170" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="FY170" t="n">
+        <v>2.08</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -90702,6 +94286,27 @@
       <c r="FR171" t="n">
         <v>11.33</v>
       </c>
+      <c r="FS171" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="FT171" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="FU171" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="FV171" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="FW171" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="FX171" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="FY171" t="n">
+        <v>2.87</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -91228,6 +94833,27 @@
       <c r="FR172" t="n">
         <v>11.55</v>
       </c>
+      <c r="FS172" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="FT172" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="FU172" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="FV172" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="FW172" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="FX172" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="FY172" t="n">
+        <v>3.46</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -91754,6 +95380,27 @@
       <c r="FR173" t="n">
         <v>11.22</v>
       </c>
+      <c r="FS173" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="FT173" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="FU173" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="FV173" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="FW173" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="FX173" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="FY173" t="n">
+        <v>3.34</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -92280,6 +95927,3856 @@
       <c r="FR174" t="n">
         <v>0</v>
       </c>
+      <c r="FS174" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="FT174" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="FU174" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="FV174" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="FW174" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="FX174" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="FY174" t="n">
+        <v>10.64</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="C175" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="D175" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="E175" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="F175" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="G175" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="H175" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="I175" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="J175" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="K175" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="L175" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="M175" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="N175" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="O175" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="P175" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="R175" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="S175" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T175" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="U175" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V175" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="W175" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="X175" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="Y175" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="Z175" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="AA175" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="AB175" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="AC175" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="AD175" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="AE175" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="AF175" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="AG175" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="AH175" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AI175" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="AJ175" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="AK175" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="AL175" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="AM175" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="AN175" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="AO175" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="AP175" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AQ175" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AR175" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="AS175" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="AT175" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="AU175" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AV175" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AW175" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="AX175" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="AY175" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AZ175" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="BA175" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="BB175" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="BC175" t="n">
+        <v>15.53</v>
+      </c>
+      <c r="BD175" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="BE175" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="BF175" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="BG175" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="BH175" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="BI175" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="BJ175" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="BK175" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="BL175" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="BM175" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="BN175" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="BO175" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="BP175" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="BQ175" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="BR175" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BS175" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT175" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="BU175" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="BV175" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="BW175" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="BX175" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BY175" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="BZ175" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="CA175" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="CB175" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="CC175" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="CD175" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="CE175" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="CF175" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="CG175" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="CH175" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="CI175" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="CJ175" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="CK175" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="CL175" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="CM175" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="CN175" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="CO175" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="CP175" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="CQ175" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="CR175" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="CS175" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="CT175" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="CU175" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="CV175" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="CW175" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CX175" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="CY175" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="CZ175" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="DA175" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="DB175" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="DC175" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="DD175" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="DE175" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="DF175" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="DG175" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="DH175" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="DI175" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="DJ175" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="DK175" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="DL175" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="DM175" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DN175" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="DO175" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="DP175" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="DQ175" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="DR175" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="DS175" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="DT175" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="DU175" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="DV175" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="DW175" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="DX175" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="DY175" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="DZ175" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="EA175" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="EB175" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="EC175" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="ED175" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="EE175" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="EF175" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="EG175" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="EH175" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="EI175" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="EJ175" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="EK175" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="EL175" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="EM175" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="EN175" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="EO175" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="EP175" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="EQ175" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="ER175" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="ES175" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="ET175" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="EU175" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="EV175" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="EW175" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="EX175" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="EY175" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="EZ175" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="FA175" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="FB175" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="FC175" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="FD175" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="FE175" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="FF175" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="FG175" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="FH175" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="FI175" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="FJ175" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="FK175" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="FL175" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="FM175" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="FN175" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="FO175" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="FP175" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="FQ175" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="FR175" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="FS175" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT175" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU175" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV175" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW175" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX175" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="C176" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="D176" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="E176" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="F176" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="G176" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="H176" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="I176" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="J176" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="K176" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="L176" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="M176" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="N176" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="O176" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="P176" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="R176" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="S176" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T176" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="U176" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V176" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="W176" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="X176" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="Y176" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="Z176" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="AA176" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="AB176" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="AC176" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="AD176" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="AE176" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="AF176" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="AG176" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="AH176" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AI176" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="AJ176" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="AK176" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="AL176" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="AM176" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="AN176" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="AO176" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="AP176" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AQ176" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AR176" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="AS176" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="AT176" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="AU176" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AV176" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AW176" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="AX176" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="AY176" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AZ176" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="BA176" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="BB176" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="BC176" t="n">
+        <v>15.53</v>
+      </c>
+      <c r="BD176" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="BE176" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="BF176" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="BG176" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="BH176" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="BI176" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="BJ176" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="BK176" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="BL176" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="BM176" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="BN176" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="BO176" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="BP176" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="BQ176" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="BR176" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BS176" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT176" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="BU176" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="BV176" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="BW176" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="BX176" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BY176" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="BZ176" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="CA176" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="CB176" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="CC176" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="CD176" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="CE176" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="CF176" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="CG176" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="CH176" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="CI176" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="CJ176" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="CK176" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="CL176" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="CM176" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="CN176" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="CO176" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="CP176" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="CQ176" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="CR176" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="CS176" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="CT176" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="CU176" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="CV176" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="CW176" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CX176" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="CY176" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="CZ176" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="DA176" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="DB176" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="DC176" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="DD176" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="DE176" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="DF176" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="DG176" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="DH176" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="DI176" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="DJ176" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="DK176" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="DL176" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="DM176" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DN176" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="DO176" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="DP176" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="DQ176" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="DR176" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="DS176" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="DT176" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="DU176" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="DV176" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="DW176" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="DX176" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="DY176" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="DZ176" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="EA176" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="EB176" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="EC176" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="ED176" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="EE176" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="EF176" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="EG176" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="EH176" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="EI176" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="EJ176" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="EK176" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="EL176" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="EM176" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="EN176" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="EO176" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="EP176" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="EQ176" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="ER176" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="ES176" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="ET176" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="EU176" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="EV176" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="EW176" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="EX176" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="EY176" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="EZ176" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="FA176" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="FB176" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="FC176" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="FD176" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="FE176" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="FF176" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="FG176" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="FH176" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="FI176" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="FJ176" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="FK176" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="FL176" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="FM176" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="FN176" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="FO176" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="FP176" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="FQ176" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="FR176" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="FS176" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT176" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU176" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV176" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW176" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX176" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="C177" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="D177" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="E177" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="F177" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="G177" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="H177" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="I177" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="J177" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="K177" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="L177" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="M177" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="N177" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="O177" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="P177" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="R177" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="S177" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T177" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="U177" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V177" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="W177" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="X177" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="Y177" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="Z177" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="AA177" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="AB177" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="AC177" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="AD177" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="AE177" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="AF177" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="AG177" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="AH177" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AI177" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="AJ177" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="AK177" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="AL177" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="AM177" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="AN177" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="AO177" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="AP177" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AQ177" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AR177" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="AS177" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="AT177" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="AU177" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AV177" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AW177" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="AX177" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="AY177" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AZ177" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="BA177" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="BB177" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="BC177" t="n">
+        <v>15.53</v>
+      </c>
+      <c r="BD177" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="BE177" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="BF177" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="BG177" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="BH177" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="BI177" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="BJ177" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="BK177" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="BL177" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="BM177" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="BN177" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="BO177" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="BP177" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="BQ177" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="BR177" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BS177" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT177" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="BU177" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="BV177" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="BW177" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="BX177" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BY177" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="BZ177" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="CA177" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="CB177" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="CC177" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="CD177" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="CE177" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="CF177" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="CG177" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="CH177" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="CI177" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="CJ177" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="CK177" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="CL177" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="CM177" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="CN177" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="CO177" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="CP177" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="CQ177" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="CR177" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="CS177" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="CT177" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="CU177" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="CV177" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="CW177" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CX177" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="CY177" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="CZ177" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="DA177" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="DB177" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="DC177" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="DD177" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="DE177" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="DF177" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="DG177" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="DH177" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="DI177" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="DJ177" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="DK177" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="DL177" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="DM177" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DN177" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="DO177" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="DP177" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="DQ177" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="DR177" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="DS177" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="DT177" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="DU177" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="DV177" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="DW177" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="DX177" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="DY177" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="DZ177" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="EA177" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="EB177" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="EC177" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="ED177" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="EE177" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="EF177" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="EG177" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="EH177" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="EI177" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="EJ177" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="EK177" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="EL177" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="EM177" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="EN177" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="EO177" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="EP177" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="EQ177" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="ER177" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="ES177" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="ET177" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="EU177" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="EV177" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="EW177" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="EX177" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="EY177" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="EZ177" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="FA177" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="FB177" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="FC177" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="FD177" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="FE177" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="FF177" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="FG177" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="FH177" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="FI177" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="FJ177" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="FK177" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="FL177" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="FM177" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="FN177" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="FO177" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="FP177" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="FQ177" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="FR177" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="FS177" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT177" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU177" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV177" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW177" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX177" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="C178" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="D178" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="E178" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="F178" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="G178" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="H178" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="I178" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="J178" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="K178" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="L178" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="M178" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="N178" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="O178" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="P178" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="R178" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="S178" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T178" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="U178" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V178" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="W178" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="X178" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="Y178" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="Z178" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="AA178" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="AB178" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="AC178" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="AD178" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="AE178" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="AF178" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="AG178" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="AH178" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AI178" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="AJ178" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="AK178" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="AL178" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="AM178" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="AN178" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="AO178" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="AP178" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AQ178" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AR178" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="AS178" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="AT178" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="AU178" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AV178" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AW178" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="AX178" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="AY178" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AZ178" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="BA178" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="BB178" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="BC178" t="n">
+        <v>15.53</v>
+      </c>
+      <c r="BD178" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="BE178" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="BF178" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="BG178" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="BH178" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="BI178" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="BJ178" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="BK178" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="BL178" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="BM178" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="BN178" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="BO178" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="BP178" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="BQ178" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="BR178" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BS178" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT178" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="BU178" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="BV178" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="BW178" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="BX178" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BY178" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="BZ178" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="CA178" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="CB178" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="CC178" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="CD178" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="CE178" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="CF178" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="CG178" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="CH178" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="CI178" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="CJ178" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="CK178" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="CL178" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="CM178" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="CN178" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="CO178" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="CP178" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="CQ178" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="CR178" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="CS178" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="CT178" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="CU178" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="CV178" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="CW178" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CX178" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="CY178" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="CZ178" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="DA178" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="DB178" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="DC178" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="DD178" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="DE178" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="DF178" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="DG178" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="DH178" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="DI178" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="DJ178" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="DK178" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="DL178" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="DM178" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DN178" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="DO178" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="DP178" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="DQ178" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="DR178" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="DS178" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="DT178" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="DU178" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="DV178" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="DW178" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="DX178" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="DY178" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="DZ178" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="EA178" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="EB178" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="EC178" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="ED178" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="EE178" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="EF178" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="EG178" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="EH178" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="EI178" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="EJ178" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="EK178" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="EL178" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="EM178" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="EN178" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="EO178" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="EP178" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="EQ178" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="ER178" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="ES178" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="ET178" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="EU178" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="EV178" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="EW178" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="EX178" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="EY178" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="EZ178" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="FA178" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="FB178" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="FC178" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="FD178" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="FE178" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="FF178" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="FG178" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="FH178" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="FI178" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="FJ178" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="FK178" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="FL178" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="FM178" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="FN178" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="FO178" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="FP178" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="FQ178" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="FR178" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="FS178" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT178" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU178" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV178" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW178" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX178" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="C179" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="D179" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="E179" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="F179" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="G179" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="H179" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="I179" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="J179" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="K179" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="L179" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="M179" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="N179" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="O179" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="P179" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="R179" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="S179" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T179" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="U179" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V179" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="W179" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="X179" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="Y179" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="Z179" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="AA179" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="AB179" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="AC179" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="AD179" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="AE179" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="AF179" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="AG179" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="AH179" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AI179" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="AJ179" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="AK179" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="AL179" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="AM179" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="AN179" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="AO179" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="AP179" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AQ179" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AR179" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="AS179" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="AT179" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="AU179" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AV179" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AW179" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="AX179" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="AY179" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AZ179" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="BA179" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="BB179" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="BC179" t="n">
+        <v>15.53</v>
+      </c>
+      <c r="BD179" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="BE179" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="BF179" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="BG179" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="BH179" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="BI179" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="BJ179" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="BK179" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="BL179" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="BM179" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="BN179" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="BO179" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="BP179" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="BQ179" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="BR179" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BS179" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT179" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="BU179" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="BV179" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="BW179" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="BX179" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BY179" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="BZ179" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="CA179" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="CB179" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="CC179" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="CD179" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="CE179" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="CF179" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="CG179" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="CH179" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="CI179" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="CJ179" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="CK179" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="CL179" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="CM179" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="CN179" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="CO179" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="CP179" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="CQ179" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="CR179" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="CS179" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="CT179" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="CU179" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="CV179" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="CW179" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CX179" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="CY179" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="CZ179" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="DA179" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="DB179" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="DC179" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="DD179" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="DE179" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="DF179" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="DG179" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="DH179" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="DI179" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="DJ179" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="DK179" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="DL179" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="DM179" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DN179" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="DO179" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="DP179" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="DQ179" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="DR179" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="DS179" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="DT179" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="DU179" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="DV179" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="DW179" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="DX179" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="DY179" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="DZ179" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="EA179" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="EB179" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="EC179" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="ED179" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="EE179" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="EF179" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="EG179" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="EH179" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="EI179" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="EJ179" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="EK179" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="EL179" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="EM179" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="EN179" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="EO179" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="EP179" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="EQ179" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="ER179" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="ES179" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="ET179" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="EU179" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="EV179" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="EW179" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="EX179" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="EY179" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="EZ179" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="FA179" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="FB179" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="FC179" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="FD179" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="FE179" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="FF179" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="FG179" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="FH179" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="FI179" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="FJ179" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="FK179" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="FL179" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="FM179" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="FN179" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="FO179" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="FP179" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="FQ179" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="FR179" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="FS179" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT179" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU179" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV179" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW179" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX179" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="C180" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="D180" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="E180" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="F180" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="G180" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="H180" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="I180" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="J180" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="K180" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="L180" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="M180" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="N180" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="O180" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="P180" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="R180" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="S180" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T180" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="U180" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V180" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="W180" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="X180" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="Y180" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="Z180" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="AA180" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="AB180" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="AC180" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="AD180" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="AE180" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="AF180" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="AG180" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="AH180" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AI180" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="AJ180" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="AK180" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="AL180" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="AM180" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="AN180" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="AO180" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="AP180" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AQ180" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AR180" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="AS180" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="AT180" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="AU180" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AV180" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AW180" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="AX180" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="AY180" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AZ180" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="BA180" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="BB180" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="BC180" t="n">
+        <v>15.53</v>
+      </c>
+      <c r="BD180" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="BE180" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="BF180" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="BG180" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="BH180" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="BI180" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="BJ180" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="BK180" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="BL180" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="BM180" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="BN180" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="BO180" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="BP180" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="BQ180" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="BR180" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BS180" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT180" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="BU180" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="BV180" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="BW180" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="BX180" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BY180" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="BZ180" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="CA180" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="CB180" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="CC180" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="CD180" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="CE180" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="CF180" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="CG180" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="CH180" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="CI180" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="CJ180" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="CK180" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="CL180" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="CM180" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="CN180" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="CO180" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="CP180" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="CQ180" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="CR180" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="CS180" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="CT180" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="CU180" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="CV180" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="CW180" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CX180" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="CY180" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="CZ180" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="DA180" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="DB180" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="DC180" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="DD180" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="DE180" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="DF180" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="DG180" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="DH180" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="DI180" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="DJ180" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="DK180" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="DL180" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="DM180" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DN180" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="DO180" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="DP180" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="DQ180" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="DR180" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="DS180" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="DT180" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="DU180" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="DV180" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="DW180" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="DX180" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="DY180" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="DZ180" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="EA180" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="EB180" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="EC180" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="ED180" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="EE180" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="EF180" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="EG180" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="EH180" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="EI180" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="EJ180" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="EK180" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="EL180" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="EM180" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="EN180" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="EO180" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="EP180" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="EQ180" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="ER180" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="ES180" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="ET180" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="EU180" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="EV180" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="EW180" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="EX180" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="EY180" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="EZ180" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="FA180" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="FB180" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="FC180" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="FD180" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="FE180" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="FF180" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="FG180" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="FH180" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="FI180" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="FJ180" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="FK180" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="FL180" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="FM180" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="FN180" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="FO180" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="FP180" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="FQ180" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="FR180" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="FS180" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT180" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU180" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV180" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW180" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX180" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="C181" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="D181" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="E181" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="F181" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="G181" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="H181" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="I181" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="J181" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="K181" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="L181" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="M181" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="N181" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="O181" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="P181" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="R181" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="S181" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T181" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="U181" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V181" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="W181" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="X181" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="Y181" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="Z181" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="AA181" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="AB181" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="AC181" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="AD181" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="AE181" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="AF181" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="AG181" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="AH181" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AI181" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="AJ181" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="AK181" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="AL181" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="AM181" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="AN181" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="AO181" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="AP181" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AQ181" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AR181" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="AS181" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="AT181" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="AU181" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AV181" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AW181" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="AX181" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="AY181" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AZ181" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="BA181" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="BB181" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="BC181" t="n">
+        <v>15.53</v>
+      </c>
+      <c r="BD181" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="BE181" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="BF181" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="BG181" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="BH181" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="BI181" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="BJ181" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="BK181" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="BL181" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="BM181" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="BN181" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="BO181" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="BP181" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="BQ181" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="BR181" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BS181" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT181" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="BU181" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="BV181" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="BW181" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="BX181" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BY181" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="BZ181" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="CA181" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="CB181" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="CC181" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="CD181" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="CE181" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="CF181" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="CG181" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="CH181" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="CI181" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="CJ181" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="CK181" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="CL181" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="CM181" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="CN181" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="CO181" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="CP181" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="CQ181" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="CR181" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="CS181" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="CT181" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="CU181" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="CV181" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="CW181" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CX181" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="CY181" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="CZ181" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="DA181" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="DB181" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="DC181" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="DD181" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="DE181" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="DF181" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="DG181" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="DH181" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="DI181" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="DJ181" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="DK181" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="DL181" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="DM181" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DN181" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="DO181" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="DP181" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="DQ181" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="DR181" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="DS181" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="DT181" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="DU181" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="DV181" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="DW181" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="DX181" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="DY181" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="DZ181" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="EA181" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="EB181" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="EC181" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="ED181" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="EE181" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="EF181" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="EG181" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="EH181" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="EI181" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="EJ181" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="EK181" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="EL181" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="EM181" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="EN181" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="EO181" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="EP181" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="EQ181" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="ER181" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="ES181" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="ET181" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="EU181" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="EV181" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="EW181" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="EX181" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="EY181" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="EZ181" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="FA181" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="FB181" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="FC181" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="FD181" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="FE181" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="FF181" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="FG181" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="FH181" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="FI181" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="FJ181" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="FK181" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="FL181" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="FM181" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="FN181" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="FO181" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="FP181" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="FQ181" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="FR181" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="FS181" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT181" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU181" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV181" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW181" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX181" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY181" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
